--- a/BOM_Proyecto.xlsx
+++ b/BOM_Proyecto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\Desktop\Carpetas\Archivos de la U\Clases\7mo semestre\Electronica 2 Victor\PCIe11414_KevinFlores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99715537-7643-4FBE-A637-DB339478AFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471F64D9-5849-4F85-92B4-02A1843B976D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4D7D3C8A-301B-4A8A-9176-E25CAE388F97}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
   <si>
     <t>Categoría</t>
   </si>
@@ -354,7 +354,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,16 +375,42 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -407,22 +433,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -759,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B76A4ACB-A583-461C-A047-0B7CFFFF248D}">
-  <dimension ref="B1:P23"/>
+  <dimension ref="B2:P24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33.21875" bestFit="1" customWidth="1"/>
@@ -774,503 +904,520 @@
     <col min="16" max="16" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
+    <row r="2" spans="2:16" ht="21" x14ac:dyDescent="0.4">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="H2" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="2:16" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
+      <c r="M2" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+    </row>
+    <row r="3" spans="2:16" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="J3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N3" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O3" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P3" s="17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="2:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="P3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
+      <c r="P4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="P5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
+      <c r="N5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>37</v>
+      <c r="I6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" ht="111" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
+      <c r="N6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>40</v>
+      <c r="I7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="P7" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="111" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
+      <c r="N7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>43</v>
+      <c r="I8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="P8" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" ht="111" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H9" s="3" t="s">
+      <c r="N8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>46</v>
+      <c r="I9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P10" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M10" s="1" t="s">
+    <row r="11" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="O11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="P10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="P12" s="4" t="s">
+      <c r="N12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="N13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="O14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="P13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="P14" s="4">
+      <c r="P14" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M16" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="P15" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M16" s="1" t="s">
+      <c r="P16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="13:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="N17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="O16" s="3" t="s">
+      <c r="O17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="P16" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="13:16" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M17" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="13:16" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="13:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="N18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="13:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="O19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P19" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="13:16" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M19" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P19" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="13:16" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="13:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="N20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P20" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="13:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="O21" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P20" s="4">
+      <c r="P21" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="13:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M21" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="P21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="13:16" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="13:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="P22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="13:16" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="13:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M23" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="N23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="13:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O23" s="3" t="s">
+      <c r="O24" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="P23" s="4">
+      <c r="P24" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="M2:P2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>